--- a/events/LaSeu_2025_WC/LaSeu_2025_WC_start.xlsx
+++ b/events/LaSeu_2025_WC/LaSeu_2025_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W589"/>
+  <dimension ref="A1:AC589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -580,7 +610,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -633,7 +663,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -686,7 +716,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -739,7 +769,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -792,7 +822,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -845,7 +875,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -898,7 +928,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -951,7 +981,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -1004,7 +1034,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -1057,7 +1087,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -1110,7 +1140,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -1163,7 +1193,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -1216,7 +1246,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -1269,7 +1299,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -1322,7 +1352,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -1375,7 +1405,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -1428,7 +1458,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -1481,7 +1511,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -1534,7 +1564,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -1587,7 +1617,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -1640,7 +1670,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -1693,7 +1723,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -1746,7 +1776,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -1799,7 +1829,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -2112,7 +2142,7 @@
           <t>MILLS Waris</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>154167</t>
         </is>
@@ -2170,7 +2200,7 @@
           <t>KRYLOVA Kseniia</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>154286</t>
         </is>
@@ -2228,7 +2258,7 @@
           <t>CULLWICK Kahlia</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>84067</t>
         </is>
@@ -2286,7 +2316,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -2344,7 +2374,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -2402,7 +2432,7 @@
           <t>NOVYSH Marina</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>153574</t>
         </is>
@@ -2460,7 +2490,7 @@
           <t>ARMANI Emilie</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>130207</t>
         </is>
@@ -2518,7 +2548,7 @@
           <t>NIAMTHONG Jaruwan</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>75405</t>
         </is>
@@ -2576,7 +2606,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -2634,7 +2664,7 @@
           <t>OLSON Beatrice</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>110818</t>
         </is>
@@ -2692,7 +2722,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -2750,7 +2780,7 @@
           <t>BELINGAR Sara</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>83888</t>
         </is>
@@ -2808,7 +2838,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -2866,7 +2896,7 @@
           <t>WU Ting-I</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>104537</t>
         </is>
@@ -2924,7 +2954,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -2982,7 +3012,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -3040,7 +3070,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -3098,7 +3128,7 @@
           <t>CHANG Chu-Han</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>51896</t>
         </is>
@@ -3156,7 +3186,7 @@
           <t>PIRRO Paulina</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>104603</t>
         </is>
@@ -3214,7 +3244,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -3272,7 +3302,7 @@
           <t>MRAZKOVA Klara</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>112649</t>
         </is>
@@ -3330,7 +3360,7 @@
           <t>MATTI Svenja</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>84161</t>
         </is>
@@ -3388,7 +3418,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -3446,7 +3476,7 @@
           <t>BRZESKA Dominika</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>93913</t>
         </is>
@@ -3504,7 +3534,7 @@
           <t>GONI Leire</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>93966</t>
         </is>
@@ -3562,7 +3592,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -3620,7 +3650,7 @@
           <t>PIETRACHA Eva</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>84043</t>
         </is>
@@ -3678,7 +3708,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -3736,7 +3766,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -3794,7 +3824,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -3852,7 +3882,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -3910,7 +3940,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -3968,7 +3998,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -4026,7 +4056,7 @@
           <t>BEKOVA Katerina</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>77167</t>
         </is>
@@ -4084,7 +4114,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -4142,7 +4172,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -4200,7 +4230,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -4258,7 +4288,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -4316,7 +4346,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -4374,7 +4404,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -4432,7 +4462,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -4490,7 +4520,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -4548,7 +4578,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -4606,7 +4636,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -4664,7 +4694,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -4722,7 +4752,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -4780,7 +4810,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -4838,7 +4868,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -4896,7 +4926,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -4954,7 +4984,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -5012,7 +5042,7 @@
           <t>ABDULLAEV Khayotbek</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>118440</t>
         </is>
@@ -5070,7 +5100,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -5128,7 +5158,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>153722</t>
         </is>
@@ -5186,7 +5216,7 @@
           <t>CHECA BARO Nil</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>153623</t>
         </is>
@@ -5244,7 +5274,7 @@
           <t>SMIRNOV Egor</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>153578</t>
         </is>
@@ -5302,7 +5332,7 @@
           <t>MANGJIT Janyawut</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>118375</t>
         </is>
@@ -5360,7 +5390,7 @@
           <t>KOZLOV Ivan</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>153572</t>
         </is>
@@ -5418,7 +5448,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -5476,7 +5506,7 @@
           <t>SNOOK George</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>83532</t>
         </is>
@@ -5534,7 +5564,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>153571</t>
         </is>
@@ -5592,7 +5622,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -5650,7 +5680,7 @@
           <t>SAYDULLAEV Samandar</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>130416</t>
         </is>
@@ -5708,7 +5738,7 @@
           <t>CHU Hung-Yu</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>142136</t>
         </is>
@@ -5766,7 +5796,7 @@
           <t>LIAO Li-Hong</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>104383</t>
         </is>
@@ -5824,7 +5854,7 @@
           <t>KOETSUK Piyanath</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>75406</t>
         </is>
@@ -5882,7 +5912,7 @@
           <t>MING Xingzhou</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>146482</t>
         </is>
@@ -5940,7 +5970,7 @@
           <t>PEREZ RINCON Alexis</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -5998,7 +6028,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -6056,7 +6086,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -6114,7 +6144,7 @@
           <t>MARTINEZ Jesus</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>118831</t>
         </is>
@@ -6172,7 +6202,7 @@
           <t>ZIELONKA Mark</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>89531</t>
         </is>
@@ -6230,7 +6260,7 @@
           <t>CANO MOLE Luca</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>142013</t>
         </is>
@@ -6288,7 +6318,7 @@
           <t>CHRISTIE-WILLIAMS John Coleman</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>106170</t>
         </is>
@@ -6346,7 +6376,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -6404,7 +6434,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -6462,7 +6492,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -6520,7 +6550,7 @@
           <t>FEDORENKO Oleksandr</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>75555</t>
         </is>
@@ -6578,7 +6608,7 @@
           <t>SOVKO Serhii</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>94235</t>
         </is>
@@ -6636,7 +6666,7 @@
           <t>BROWN Jake</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>86247</t>
         </is>
@@ -6694,7 +6724,7 @@
           <t>JEMAI Salim</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>133333</t>
         </is>
@@ -6752,7 +6782,7 @@
           <t>STEINBRENNER Max</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>142180</t>
         </is>
@@ -6810,7 +6840,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -6868,7 +6898,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -6926,7 +6956,7 @@
           <t>CUNHA Joao</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>76853</t>
         </is>
@@ -6984,7 +7014,7 @@
           <t>WU Shao-Hsuan</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>43104</t>
         </is>
@@ -7042,7 +7072,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -7100,7 +7130,7 @@
           <t>VERNON Reilly</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>130120</t>
         </is>
@@ -7158,7 +7188,7 @@
           <t>IVCHENKO Artem</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>118746</t>
         </is>
@@ -7216,7 +7246,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -7274,7 +7304,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -7332,7 +7362,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -7390,7 +7420,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -7448,7 +7478,7 @@
           <t>DIETZ Enrico</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>104604</t>
         </is>
@@ -7506,7 +7536,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -7564,7 +7594,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -7622,7 +7652,7 @@
           <t>BARTA Jan</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>75448</t>
         </is>
@@ -7680,7 +7710,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -7738,7 +7768,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -7796,7 +7826,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -7854,7 +7884,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -7912,7 +7942,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -7970,7 +8000,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -8028,7 +8058,7 @@
           <t>LOCNIKAR Jan</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>83922</t>
         </is>
@@ -8086,7 +8116,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -8144,7 +8174,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -8202,7 +8232,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -8260,7 +8290,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -8318,7 +8348,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -8376,7 +8406,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -8434,7 +8464,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -8492,7 +8522,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -8550,7 +8580,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -8608,7 +8638,7 @@
           <t>BEDA Marcello</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>39899</t>
         </is>
@@ -8666,7 +8696,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -8724,7 +8754,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -8782,7 +8812,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -8840,7 +8870,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -8898,7 +8928,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -8956,7 +8986,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -9014,7 +9044,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -9072,7 +9102,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -9130,7 +9160,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -9188,7 +9218,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -9246,7 +9276,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -9304,7 +9334,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -9362,7 +9392,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -9420,7 +9450,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -9478,7 +9508,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -9536,7 +9566,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -9594,7 +9624,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -9652,7 +9682,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -9710,7 +9740,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -9768,7 +9798,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -9826,7 +9856,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -9884,7 +9914,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -9952,7 +9982,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10020,7 +10050,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -10088,7 +10118,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -10156,7 +10186,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -10224,7 +10254,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -10292,7 +10322,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -10360,7 +10390,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -10428,7 +10458,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -10496,7 +10526,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -10564,7 +10594,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -10632,7 +10662,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -10700,7 +10730,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -10768,7 +10798,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -10836,7 +10866,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -10904,7 +10934,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -10972,7 +11002,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -11040,7 +11070,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -11108,7 +11138,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -11176,7 +11206,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -11244,7 +11274,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -11312,7 +11342,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -11380,7 +11410,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -11448,7 +11478,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -11516,7 +11546,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -11829,7 +11859,7 @@
           <t>CHOMKOGSUNG Kanda</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>118371</t>
         </is>
@@ -11887,7 +11917,7 @@
           <t>NOVYSH Marina</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>153574</t>
         </is>
@@ -11945,7 +11975,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>153573</t>
         </is>
@@ -12003,7 +12033,7 @@
           <t>YANG Ting</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>146484</t>
         </is>
@@ -12061,7 +12091,7 @@
           <t>CHOU Chih-Chin</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>68975</t>
         </is>
@@ -12119,7 +12149,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -12177,7 +12207,7 @@
           <t>XU Jiaqi</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>142190</t>
         </is>
@@ -12235,7 +12265,7 @@
           <t>CHUNG Yu-Han</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>51895</t>
         </is>
@@ -12293,7 +12323,7 @@
           <t>CULLWICK Kahlia</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>84067</t>
         </is>
@@ -12351,7 +12381,7 @@
           <t>WU Yishan</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>130289</t>
         </is>
@@ -12409,7 +12439,7 @@
           <t>MASSARENTI Carolina</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>142089</t>
         </is>
@@ -12467,7 +12497,7 @@
           <t>BELINGAR Sara</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>83888</t>
         </is>
@@ -12525,7 +12555,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -12583,7 +12613,7 @@
           <t>RAPPE Kimberley</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>93984</t>
         </is>
@@ -12641,7 +12671,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -12699,7 +12729,7 @@
           <t>MORENOVA Adriana</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>98979</t>
         </is>
@@ -12757,7 +12787,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -12815,7 +12845,7 @@
           <t>ROISIN Laurene</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>76198</t>
         </is>
@@ -12873,7 +12903,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -12931,7 +12961,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -12989,7 +13019,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -13047,7 +13077,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -13105,7 +13135,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -13163,7 +13193,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -13221,7 +13251,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -13279,7 +13309,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -13337,7 +13367,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -13395,7 +13425,7 @@
           <t>DELASSUS Doriane</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>84178</t>
         </is>
@@ -13453,7 +13483,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -13511,7 +13541,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -13569,7 +13599,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -13627,7 +13657,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -13685,7 +13715,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -13743,7 +13773,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -13801,7 +13831,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -13859,7 +13889,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -13917,7 +13947,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -13975,7 +14005,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -14033,7 +14063,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -14091,7 +14121,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -14149,7 +14179,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -14207,7 +14237,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -14265,7 +14295,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -14323,7 +14353,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -14381,7 +14411,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -14439,7 +14469,7 @@
           <t>SMIRNOV Egor</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>153578</t>
         </is>
@@ -14497,7 +14527,7 @@
           <t>NG Wee Meng</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>142119</t>
         </is>
@@ -14555,7 +14585,7 @@
           <t>SHEN Yufei</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>146476</t>
         </is>
@@ -14613,7 +14643,7 @@
           <t>KHARLAMTSEV Aleksandr</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>153576</t>
         </is>
@@ -14671,7 +14701,7 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>153577</t>
         </is>
@@ -14729,7 +14759,7 @@
           <t>ONGCHIT Nantipat</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>118373</t>
         </is>
@@ -14787,7 +14817,7 @@
           <t>PHUTTRAKSA Chonlasit</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>84395</t>
         </is>
@@ -14845,7 +14875,7 @@
           <t>KURBANALIEV Sherzod</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>112912</t>
         </is>
@@ -14903,7 +14933,7 @@
           <t>TSENG Hsin-Kuang</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>142135</t>
         </is>
@@ -14961,7 +14991,7 @@
           <t>GEVAERT Tyler</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>118726</t>
         </is>
@@ -15019,7 +15049,7 @@
           <t>CHANG Fu-Hua</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>122609</t>
         </is>
@@ -15077,7 +15107,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -15135,7 +15165,7 @@
           <t>KOETSUK Piyanath</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>75406</t>
         </is>
@@ -15193,7 +15223,7 @@
           <t>BUKANOV Abubakir</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>75374</t>
         </is>
@@ -15251,7 +15281,7 @@
           <t>SENIOR James</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>104365</t>
         </is>
@@ -15309,7 +15339,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -15367,7 +15397,7 @@
           <t>ANDERSON Finn</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>83516</t>
         </is>
@@ -15425,7 +15455,7 @@
           <t>ROZENTALS Klass Francisks</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>142203</t>
         </is>
@@ -15483,7 +15513,7 @@
           <t>WU Jung-Cheng</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>75823</t>
         </is>
@@ -15541,7 +15571,7 @@
           <t>LOOS Soren</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>130162</t>
         </is>
@@ -15599,7 +15629,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -15657,7 +15687,7 @@
           <t>SAITO Shota</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>96090</t>
         </is>
@@ -15715,7 +15745,7 @@
           <t>FRANCIS Nathaniel</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>87396</t>
         </is>
@@ -15773,7 +15803,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -15831,7 +15861,7 @@
           <t>ZIMMERMANN Niels</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>112606</t>
         </is>
@@ -15889,7 +15919,7 @@
           <t>ROYLE Luc</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>97349</t>
         </is>
@@ -15947,7 +15977,7 @@
           <t>DIAZ Oier</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>118826</t>
         </is>
@@ -16005,7 +16035,7 @@
           <t>WIERCIOCH Michal</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
@@ -16063,7 +16093,7 @@
           <t>ZHANG Peng</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>63799</t>
         </is>
@@ -16121,7 +16151,7 @@
           <t>ROSS Benjamin</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>104423</t>
         </is>
@@ -16179,7 +16209,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -16237,7 +16267,7 @@
           <t>NOWOBILSKI Szymon</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>75737</t>
         </is>
@@ -16295,7 +16325,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -16353,7 +16383,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -16411,7 +16441,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -16469,7 +16499,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -16527,7 +16557,7 @@
           <t>VICENTE Marc</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>106068</t>
         </is>
@@ -16585,7 +16615,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -16643,7 +16673,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -16701,7 +16731,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -16759,7 +16789,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -16817,7 +16847,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -16875,7 +16905,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -16933,7 +16963,7 @@
           <t>SPAGNOL Marino</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>104653</t>
         </is>
@@ -16991,7 +17021,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -17049,7 +17079,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -17107,7 +17137,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -17165,7 +17195,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -17223,7 +17253,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -17281,7 +17311,7 @@
           <t>KRAL Adam</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>83772</t>
         </is>
@@ -17339,7 +17369,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -17397,7 +17427,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -17455,7 +17485,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -17513,7 +17543,7 @@
           <t>BARZON Martino</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>83978</t>
         </is>
@@ -17571,7 +17601,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -17629,7 +17659,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -17687,7 +17717,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -17745,7 +17775,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -17803,7 +17833,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -17861,7 +17891,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -17919,7 +17949,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -17977,7 +18007,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -18035,7 +18065,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -18093,7 +18123,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -18151,7 +18181,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -18209,7 +18239,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -18267,7 +18297,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -18325,7 +18355,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -18393,7 +18423,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -18461,7 +18491,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -18529,7 +18559,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -18597,7 +18627,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -18665,7 +18695,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -18733,7 +18763,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18801,7 +18831,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -18869,7 +18899,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -18937,7 +18967,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -19005,7 +19035,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -19073,7 +19103,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -19141,7 +19171,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -19209,7 +19239,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -19277,7 +19307,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -19345,7 +19375,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -19413,7 +19443,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -19481,7 +19511,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -19549,7 +19579,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -19617,7 +19647,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -19685,7 +19715,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -19753,7 +19783,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -19821,7 +19851,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -19889,7 +19919,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -19957,7 +19987,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -20247,7 +20277,7 @@
           <t>CHOMKOGSUNG Kanda</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>118371</t>
         </is>
@@ -20368,7 +20398,7 @@
           <t>MILLS Waris</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>154167</t>
         </is>
@@ -20431,7 +20461,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -20494,7 +20524,7 @@
           <t>KRYLOVA Kseniia</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>154286</t>
         </is>
@@ -20557,7 +20587,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>153573</t>
         </is>
@@ -20620,7 +20650,7 @@
           <t>NIAMTHONG Jaruwan</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>75405</t>
         </is>
@@ -20683,7 +20713,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -20746,7 +20776,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -20809,7 +20839,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -20872,7 +20902,7 @@
           <t>OLSON Beatrice</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>110818</t>
         </is>
@@ -20935,7 +20965,7 @@
           <t>PITCHER FARRELL Cleo</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>106358</t>
         </is>
@@ -20998,7 +21028,7 @@
           <t>ARMANI Emilie</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>130207</t>
         </is>
@@ -21061,7 +21091,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -21124,7 +21154,7 @@
           <t>MATTI Svenja</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>84161</t>
         </is>
@@ -21187,7 +21217,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -21250,7 +21280,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -21313,7 +21343,7 @@
           <t>SAMKOVA Olga</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>105999</t>
         </is>
@@ -21376,7 +21406,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -21439,7 +21469,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -21502,7 +21532,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -21565,7 +21595,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -21628,7 +21658,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -21691,7 +21721,7 @@
           <t>O'CALLAGHAN Georgia</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>93787</t>
         </is>
@@ -21754,7 +21784,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -21817,7 +21847,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -21880,7 +21910,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -21943,7 +21973,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -22006,7 +22036,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -22069,7 +22099,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -22132,7 +22162,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -22195,7 +22225,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -22258,7 +22288,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -22321,7 +22351,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -22384,7 +22414,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -22447,7 +22477,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -22510,7 +22540,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -22573,7 +22603,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -22636,7 +22666,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -22699,7 +22729,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -22762,7 +22792,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -22825,7 +22855,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -22888,7 +22918,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -22951,7 +22981,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -23014,7 +23044,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -23077,7 +23107,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -23140,7 +23170,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -23203,7 +23233,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -23266,7 +23296,7 @@
           <t>ISLAMOV Daniyar</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>118438</t>
         </is>
@@ -23329,7 +23359,7 @@
           <t>SMIRNOV Egor</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>153578</t>
         </is>
@@ -23392,7 +23422,7 @@
           <t>PHUTTRAKSA Chonlasit</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>84395</t>
         </is>
@@ -23455,7 +23485,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>153722</t>
         </is>
@@ -23518,7 +23548,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -23581,7 +23611,7 @@
           <t>NDIAYE Youssouf Wally</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>154164</t>
         </is>
@@ -23644,7 +23674,7 @@
           <t>MANGJIT Janyawut</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>118375</t>
         </is>
@@ -23707,7 +23737,7 @@
           <t>GUBENKO Nikita</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>153571</t>
         </is>
@@ -23770,7 +23800,7 @@
           <t>KOZLOV Ivan</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>153572</t>
         </is>
@@ -23833,7 +23863,7 @@
           <t>KOETSUK Piyanath</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>75406</t>
         </is>
@@ -23896,7 +23926,7 @@
           <t>CHECA BARO Nil</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>153623</t>
         </is>
@@ -23959,7 +23989,7 @@
           <t>FRANCIS Nathaniel</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>87396</t>
         </is>
@@ -24022,7 +24052,7 @@
           <t>SNOOK George</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>83532</t>
         </is>
@@ -24085,7 +24115,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -24148,7 +24178,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -24211,7 +24241,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -24274,7 +24304,7 @@
           <t>STEINBRENNER Max</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>142180</t>
         </is>
@@ -24337,7 +24367,7 @@
           <t>MING Xingzhou</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>146482</t>
         </is>
@@ -24400,7 +24430,7 @@
           <t>LOCNIKAR Jan</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>83922</t>
         </is>
@@ -24463,7 +24493,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -24526,7 +24556,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -24589,7 +24619,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -24652,7 +24682,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -24715,7 +24745,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -24778,7 +24808,7 @@
           <t>CANO MOLE Luca</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>142013</t>
         </is>
@@ -24841,7 +24871,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -24904,7 +24934,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -24967,7 +24997,7 @@
           <t>ROZENTALS Klass Francisks</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>142203</t>
         </is>
@@ -25030,7 +25060,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -25093,7 +25123,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -25156,7 +25186,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -25219,7 +25249,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -25282,7 +25312,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -25345,7 +25375,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -25408,7 +25438,7 @@
           <t>CUNHA Joao</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>76853</t>
         </is>
@@ -25471,7 +25501,7 @@
           <t>ZIELONKA Mark</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>89531</t>
         </is>
@@ -25534,7 +25564,7 @@
           <t>SOVKO Serhii</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>94235</t>
         </is>
@@ -25597,7 +25627,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -25660,7 +25690,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -25723,7 +25753,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -25786,7 +25816,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -25849,7 +25879,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -25912,7 +25942,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -25975,7 +26005,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -26038,7 +26068,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -26101,7 +26131,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -26164,7 +26194,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -26227,7 +26257,7 @@
           <t>MARTINEZ Jesus</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>118831</t>
         </is>
@@ -26290,7 +26320,7 @@
           <t>IVCHENKO Artem</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>118746</t>
         </is>
@@ -26353,7 +26383,7 @@
           <t>PEREZ RINCON Alexis</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -26416,7 +26446,7 @@
           <t>SAVLI Jakob</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>96696</t>
         </is>
@@ -26479,7 +26509,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -26542,7 +26572,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -26605,7 +26635,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -26668,7 +26698,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -26731,7 +26761,7 @@
           <t>ROELLER Tillmann</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>83990</t>
         </is>
@@ -26794,7 +26824,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -26857,7 +26887,7 @@
           <t>JEMAI Salim</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>133333</t>
         </is>
@@ -26920,7 +26950,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -26983,7 +27013,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -27046,7 +27076,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -27109,7 +27139,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -27172,7 +27202,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -27235,7 +27265,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -27298,7 +27328,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -27361,7 +27391,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -27424,7 +27454,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -27487,7 +27517,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -27550,7 +27580,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -27613,7 +27643,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -27676,7 +27706,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -27739,7 +27769,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -27802,7 +27832,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -27865,7 +27895,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -27928,7 +27958,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -27991,7 +28021,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -28054,7 +28084,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -28117,7 +28147,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -28180,7 +28210,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -28243,7 +28273,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -28306,7 +28336,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -28369,7 +28399,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -28437,7 +28467,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -28505,7 +28535,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -28573,7 +28603,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -28641,7 +28671,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>153573</t>
         </is>
@@ -28709,7 +28739,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -28777,7 +28807,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -28845,7 +28875,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -28913,7 +28943,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -29044,7 +29074,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -29112,7 +29142,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -29180,7 +29210,7 @@
           <t>KRYLOVA Kseniia</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>154286</t>
         </is>
@@ -29248,7 +29278,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -29316,7 +29346,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -29384,7 +29414,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -29452,7 +29482,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -29520,7 +29550,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -29588,7 +29618,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -29656,7 +29686,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -29724,7 +29754,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -29792,7 +29822,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -29860,7 +29890,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -29928,7 +29958,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -29996,7 +30026,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -30064,7 +30094,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -30132,7 +30162,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -30200,7 +30230,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -30268,7 +30298,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -30336,7 +30366,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -30404,7 +30434,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -30472,7 +30502,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -30540,7 +30570,7 @@
           <t>MATTI Svenja</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>84161</t>
         </is>
@@ -30608,7 +30638,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -30676,7 +30706,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -30744,7 +30774,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -30812,7 +30842,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -30880,7 +30910,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -30948,7 +30978,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -31016,7 +31046,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -31084,7 +31114,7 @@
           <t>SAVLI Jakob</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>96696</t>
         </is>
@@ -31152,7 +31182,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -31220,7 +31250,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -31288,7 +31318,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -31356,7 +31386,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -31424,7 +31454,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -31492,7 +31522,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -31560,7 +31590,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -31628,7 +31658,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -31696,7 +31726,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -31764,7 +31794,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -31832,7 +31862,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -31900,7 +31930,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -31968,7 +31998,7 @@
           <t>KOZLOV Ivan</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>153572</t>
         </is>
@@ -32036,7 +32066,7 @@
           <t>LOCNIKAR Jan</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>83922</t>
         </is>
@@ -32104,7 +32134,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -32172,7 +32202,7 @@
           <t>IVCHENKO Artem</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>118746</t>
         </is>
@@ -32240,7 +32270,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -32308,7 +32338,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -32376,7 +32406,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -32444,7 +32474,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -32512,7 +32542,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -32580,7 +32610,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -32648,7 +32678,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -32716,7 +32746,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -32784,7 +32814,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -32852,7 +32882,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -32920,7 +32950,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -32988,7 +33018,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>153573</t>
         </is>
@@ -33056,7 +33086,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -33124,7 +33154,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -33192,7 +33222,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -33260,7 +33290,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -33328,7 +33358,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -33396,7 +33426,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -33464,7 +33494,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -33532,7 +33562,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -33600,7 +33630,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -33668,7 +33698,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -33736,7 +33766,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -33804,7 +33834,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -33872,7 +33902,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -33940,7 +33970,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -34008,7 +34038,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -34076,7 +34106,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -34144,7 +34174,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -34212,7 +34242,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -34280,7 +34310,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -34348,7 +34378,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -34416,7 +34446,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -34484,7 +34514,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -34552,7 +34582,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -34620,7 +34650,7 @@
           <t>IVCHENKO Artem</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>118746</t>
         </is>
@@ -34688,7 +34718,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -34756,7 +34786,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -34824,7 +34854,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -34892,7 +34922,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -34960,7 +34990,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -35028,7 +35058,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -35096,7 +35126,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -35164,7 +35194,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -35232,7 +35262,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -35300,7 +35330,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -35368,7 +35398,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -35436,7 +35466,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -35504,7 +35534,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -35572,7 +35602,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -35640,7 +35670,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -35708,7 +35738,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -35776,7 +35806,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -35844,7 +35874,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -35912,7 +35942,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -35980,7 +36010,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -36058,7 +36088,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -36136,7 +36166,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -36214,7 +36244,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -36292,7 +36322,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -36370,7 +36400,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -36448,7 +36478,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -36526,7 +36556,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -36604,7 +36634,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -36682,7 +36712,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -36760,7 +36790,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -36838,7 +36868,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -36916,7 +36946,7 @@
           <t>NDIAYE Youssouf Wally</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>154164</t>
         </is>

--- a/events/LaSeu_2025_WC/LaSeu_2025_WC_start.xlsx
+++ b/events/LaSeu_2025_WC/LaSeu_2025_WC_start.xlsx
@@ -20335,6 +20335,11 @@
       <c r="K337" t="n">
         <v>336</v>
       </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R337" t="inlineStr">
         <is>
           <t>LOGACHEVA Taisiia</t>
@@ -20393,6 +20398,11 @@
       <c r="K338" t="n">
         <v>337</v>
       </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="R338" t="inlineStr">
         <is>
           <t>MILLS Waris</t>
@@ -20456,6 +20466,11 @@
       <c r="K339" t="n">
         <v>338</v>
       </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R339" t="inlineStr">
         <is>
           <t>LUKNAROVA Emanuela</t>
@@ -20519,6 +20534,11 @@
       <c r="K340" t="n">
         <v>339</v>
       </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R340" t="inlineStr">
         <is>
           <t>KRYLOVA Kseniia</t>
@@ -20582,6 +20602,11 @@
       <c r="K341" t="n">
         <v>340</v>
       </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R341" t="inlineStr">
         <is>
           <t>MINAZOVA Alsu</t>
@@ -20708,6 +20733,11 @@
       <c r="K343" t="n">
         <v>342</v>
       </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R343" t="inlineStr">
         <is>
           <t>CHEN Lin</t>
@@ -20771,6 +20801,11 @@
       <c r="K344" t="n">
         <v>343</v>
       </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R344" t="inlineStr">
         <is>
           <t>HERZOG Andrea</t>
@@ -20834,6 +20869,11 @@
       <c r="K345" t="n">
         <v>344</v>
       </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="R345" t="inlineStr">
         <is>
           <t>BAYN Nele</t>
@@ -20897,6 +20937,11 @@
       <c r="K346" t="n">
         <v>345</v>
       </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R346" t="inlineStr">
         <is>
           <t>OLSON Beatrice</t>
@@ -20960,6 +21005,11 @@
       <c r="K347" t="n">
         <v>346</v>
       </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R347" t="inlineStr">
         <is>
           <t>PITCHER FARRELL Cleo</t>
@@ -21023,6 +21073,11 @@
       <c r="K348" t="n">
         <v>347</v>
       </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R348" t="inlineStr">
         <is>
           <t>ARMANI Emilie</t>
@@ -21086,6 +21141,11 @@
       <c r="K349" t="n">
         <v>348</v>
       </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R349" t="inlineStr">
         <is>
           <t>SOMMERNES Iris</t>
@@ -21149,6 +21209,11 @@
       <c r="K350" t="n">
         <v>349</v>
       </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R350" t="inlineStr">
         <is>
           <t>MATTI Svenja</t>
@@ -21212,6 +21277,11 @@
       <c r="K351" t="n">
         <v>350</v>
       </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R351" t="inlineStr">
         <is>
           <t>PELLICER CHICA Laura</t>
@@ -21275,6 +21345,11 @@
       <c r="K352" t="n">
         <v>351</v>
       </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R352" t="inlineStr">
         <is>
           <t>WAN Shunfang</t>
@@ -21338,6 +21413,11 @@
       <c r="K353" t="n">
         <v>352</v>
       </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R353" t="inlineStr">
         <is>
           <t>SAMKOVA Olga</t>
@@ -21401,6 +21481,11 @@
       <c r="K354" t="n">
         <v>353</v>
       </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R354" t="inlineStr">
         <is>
           <t>GORA Aleksandra</t>
@@ -21464,6 +21549,11 @@
       <c r="K355" t="n">
         <v>354</v>
       </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R355" t="inlineStr">
         <is>
           <t>SORRIBES Laia</t>
@@ -21590,6 +21680,11 @@
       <c r="K357" t="n">
         <v>356</v>
       </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R357" t="inlineStr">
         <is>
           <t>LEAVER Lois</t>
@@ -21653,6 +21748,11 @@
       <c r="K358" t="n">
         <v>357</v>
       </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R358" t="inlineStr">
         <is>
           <t>BALDONI Lea</t>
@@ -21716,6 +21816,11 @@
       <c r="K359" t="n">
         <v>358</v>
       </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="R359" t="inlineStr">
         <is>
           <t>O'CALLAGHAN Georgia</t>
@@ -21779,6 +21884,11 @@
       <c r="K360" t="n">
         <v>359</v>
       </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R360" t="inlineStr">
         <is>
           <t>ALTMAN Marcella</t>
@@ -21842,6 +21952,11 @@
       <c r="K361" t="n">
         <v>360</v>
       </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R361" t="inlineStr">
         <is>
           <t>PANKOVA Zuzana</t>
@@ -21905,6 +22020,11 @@
       <c r="K362" t="n">
         <v>361</v>
       </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R362" t="inlineStr">
         <is>
           <t>STANOVSKA Sona</t>
@@ -21968,6 +22088,11 @@
       <c r="K363" t="n">
         <v>362</v>
       </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R363" t="inlineStr">
         <is>
           <t>HILGERTOVA Amalie</t>
@@ -22031,6 +22156,11 @@
       <c r="K364" t="n">
         <v>363</v>
       </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R364" t="inlineStr">
         <is>
           <t>NOVAK Ajda</t>
@@ -22094,6 +22224,11 @@
       <c r="K365" t="n">
         <v>364</v>
       </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R365" t="inlineStr">
         <is>
           <t>SABATTINI Chiara</t>
@@ -22157,6 +22292,11 @@
       <c r="K366" t="n">
         <v>365</v>
       </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R366" t="inlineStr">
         <is>
           <t>HOCEVAR Eva Alina</t>
@@ -22220,6 +22360,11 @@
       <c r="K367" t="n">
         <v>366</v>
       </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R367" t="inlineStr">
         <is>
           <t>LAZKANO Miren</t>
@@ -22346,6 +22491,11 @@
       <c r="K369" t="n">
         <v>368</v>
       </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R369" t="inlineStr">
         <is>
           <t>XIE Xueting</t>
@@ -22409,6 +22559,11 @@
       <c r="K370" t="n">
         <v>369</v>
       </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R370" t="inlineStr">
         <is>
           <t>US Viktoriia</t>
@@ -22472,6 +22627,11 @@
       <c r="K371" t="n">
         <v>370</v>
       </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R371" t="inlineStr">
         <is>
           <t>KNEBLOVA Tereza</t>
@@ -22535,6 +22695,11 @@
       <c r="K372" t="n">
         <v>371</v>
       </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R372" t="inlineStr">
         <is>
           <t>DORIA Monica</t>
@@ -22598,6 +22763,11 @@
       <c r="K373" t="n">
         <v>372</v>
       </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R373" t="inlineStr">
         <is>
           <t>FOX Jessica</t>
@@ -22661,6 +22831,11 @@
       <c r="K374" t="n">
         <v>373</v>
       </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="R374" t="inlineStr">
         <is>
           <t>SETCHELL Nikita</t>
@@ -22724,6 +22899,11 @@
       <c r="K375" t="n">
         <v>374</v>
       </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R375" t="inlineStr">
         <is>
           <t>VUITTON Emma</t>
@@ -22787,6 +22967,11 @@
       <c r="K376" t="n">
         <v>375</v>
       </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R376" t="inlineStr">
         <is>
           <t>LEIBFARTH Evy</t>
@@ -22850,6 +23035,11 @@
       <c r="K377" t="n">
         <v>376</v>
       </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R377" t="inlineStr">
         <is>
           <t>FUNK Ricarda</t>
@@ -22913,6 +23103,11 @@
       <c r="K378" t="n">
         <v>377</v>
       </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R378" t="inlineStr">
         <is>
           <t>MARX Alena</t>
@@ -22976,6 +23171,11 @@
       <c r="K379" t="n">
         <v>378</v>
       </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R379" t="inlineStr">
         <is>
           <t>CHOURRAUT Maialen</t>
@@ -23039,6 +23239,11 @@
       <c r="K380" t="n">
         <v>379</v>
       </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R380" t="inlineStr">
         <is>
           <t>FOX Noemie</t>
@@ -23102,6 +23307,11 @@
       <c r="K381" t="n">
         <v>380</v>
       </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R381" t="inlineStr">
         <is>
           <t>PRIGENT Camille</t>
@@ -23165,6 +23375,11 @@
       <c r="K382" t="n">
         <v>381</v>
       </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R382" t="inlineStr">
         <is>
           <t>HUG Angele</t>
@@ -23228,6 +23443,11 @@
       <c r="K383" t="n">
         <v>382</v>
       </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R383" t="inlineStr">
         <is>
           <t>WOODS Kimberley</t>
@@ -23291,6 +23511,11 @@
       <c r="K384" t="n">
         <v>383</v>
       </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="R384" t="inlineStr">
         <is>
           <t>ISLAMOV Daniyar</t>
@@ -23354,6 +23579,11 @@
       <c r="K385" t="n">
         <v>384</v>
       </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R385" t="inlineStr">
         <is>
           <t>SMIRNOV Egor</t>
@@ -23480,6 +23710,11 @@
       <c r="K387" t="n">
         <v>386</v>
       </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R387" t="inlineStr">
         <is>
           <t>EIGEL Pavel</t>
@@ -23543,6 +23778,11 @@
       <c r="K388" t="n">
         <v>387</v>
       </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
       <c r="R388" t="inlineStr">
         <is>
           <t>ONG Jun Yi</t>
@@ -23606,6 +23846,11 @@
       <c r="K389" t="n">
         <v>388</v>
       </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="R389" t="inlineStr">
         <is>
           <t>NDIAYE Youssouf Wally</t>
@@ -23732,6 +23977,11 @@
       <c r="K391" t="n">
         <v>390</v>
       </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="R391" t="inlineStr">
         <is>
           <t>GUBENKO Nikita</t>
@@ -23795,6 +24045,11 @@
       <c r="K392" t="n">
         <v>391</v>
       </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R392" t="inlineStr">
         <is>
           <t>KOZLOV Ivan</t>
@@ -23921,6 +24176,11 @@
       <c r="K394" t="n">
         <v>393</v>
       </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="R394" t="inlineStr">
         <is>
           <t>CHECA BARO Nil</t>
@@ -23984,6 +24244,11 @@
       <c r="K395" t="n">
         <v>394</v>
       </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="R395" t="inlineStr">
         <is>
           <t>FRANCIS Nathaniel</t>
@@ -24047,6 +24312,11 @@
       <c r="K396" t="n">
         <v>395</v>
       </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="R396" t="inlineStr">
         <is>
           <t>SNOOK George</t>
@@ -24110,6 +24380,11 @@
       <c r="K397" t="n">
         <v>396</v>
       </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R397" t="inlineStr">
         <is>
           <t>MUTO Yusuke</t>
@@ -24173,6 +24448,11 @@
       <c r="K398" t="n">
         <v>397</v>
       </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="R398" t="inlineStr">
         <is>
           <t>WEWEGE Donovan</t>
@@ -24236,6 +24516,11 @@
       <c r="K399" t="n">
         <v>398</v>
       </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="R399" t="inlineStr">
         <is>
           <t>TEMIRGALIEV Djanibek</t>
@@ -24299,6 +24584,11 @@
       <c r="K400" t="n">
         <v>399</v>
       </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="R400" t="inlineStr">
         <is>
           <t>STEINBRENNER Max</t>
@@ -24362,6 +24652,11 @@
       <c r="K401" t="n">
         <v>400</v>
       </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="R401" t="inlineStr">
         <is>
           <t>MING Xingzhou</t>
@@ -24425,6 +24720,11 @@
       <c r="K402" t="n">
         <v>401</v>
       </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R402" t="inlineStr">
         <is>
           <t>LOCNIKAR Jan</t>
@@ -24488,6 +24788,11 @@
       <c r="K403" t="n">
         <v>402</v>
       </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="R403" t="inlineStr">
         <is>
           <t>MAPELLI Guilherme</t>
@@ -24551,6 +24856,11 @@
       <c r="K404" t="n">
         <v>403</v>
       </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R404" t="inlineStr">
         <is>
           <t>ZHANG Hejie</t>
@@ -24614,6 +24924,11 @@
       <c r="K405" t="n">
         <v>404</v>
       </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R405" t="inlineStr">
         <is>
           <t>RUDORFER Martin</t>
@@ -24677,6 +24992,11 @@
       <c r="K406" t="n">
         <v>405</v>
       </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="R406" t="inlineStr">
         <is>
           <t>GONSENICA Adam</t>
@@ -24740,6 +25060,11 @@
       <c r="K407" t="n">
         <v>406</v>
       </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="R407" t="inlineStr">
         <is>
           <t>TANAKA Yuuki</t>
@@ -24803,6 +25128,11 @@
       <c r="K408" t="n">
         <v>407</v>
       </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="R408" t="inlineStr">
         <is>
           <t>CANO MOLE Luca</t>
@@ -24866,6 +25196,11 @@
       <c r="K409" t="n">
         <v>408</v>
       </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="R409" t="inlineStr">
         <is>
           <t>EICHFELD Casey</t>
@@ -24929,6 +25264,11 @@
       <c r="K410" t="n">
         <v>409</v>
       </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R410" t="inlineStr">
         <is>
           <t>GRIGAR Jakub</t>
@@ -24992,6 +25332,11 @@
       <c r="K411" t="n">
         <v>410</v>
       </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="R411" t="inlineStr">
         <is>
           <t>ROZENTALS Klass Francisks</t>
@@ -25055,6 +25400,11 @@
       <c r="K412" t="n">
         <v>411</v>
       </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R412" t="inlineStr">
         <is>
           <t>HAYLETT Ben</t>
@@ -25118,6 +25468,11 @@
       <c r="K413" t="n">
         <v>412</v>
       </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="R413" t="inlineStr">
         <is>
           <t>BARAT Andy</t>
@@ -25181,6 +25536,11 @@
       <c r="K414" t="n">
         <v>413</v>
       </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="R414" t="inlineStr">
         <is>
           <t>SARAMANDIF Terence</t>
@@ -25244,6 +25604,11 @@
       <c r="K415" t="n">
         <v>414</v>
       </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R415" t="inlineStr">
         <is>
           <t>JACOB Lucas</t>
@@ -25307,6 +25672,11 @@
       <c r="K416" t="n">
         <v>415</v>
       </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R416" t="inlineStr">
         <is>
           <t>UKALOVIC Thomas</t>
@@ -25370,6 +25740,11 @@
       <c r="K417" t="n">
         <v>416</v>
       </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R417" t="inlineStr">
         <is>
           <t>HUANG Liman</t>
@@ -25433,6 +25808,11 @@
       <c r="K418" t="n">
         <v>417</v>
       </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="R418" t="inlineStr">
         <is>
           <t>CUNHA Joao</t>
@@ -25496,6 +25876,11 @@
       <c r="K419" t="n">
         <v>418</v>
       </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R419" t="inlineStr">
         <is>
           <t>ZIELONKA Mark</t>
@@ -25559,6 +25944,11 @@
       <c r="K420" t="n">
         <v>419</v>
       </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="R420" t="inlineStr">
         <is>
           <t>SOVKO Serhii</t>
@@ -25622,6 +26012,11 @@
       <c r="K421" t="n">
         <v>420</v>
       </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="R421" t="inlineStr">
         <is>
           <t>BOYD Trevor</t>
@@ -25685,6 +26080,11 @@
       <c r="K422" t="n">
         <v>421</v>
       </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="R422" t="inlineStr">
         <is>
           <t>JEGOU Liam</t>
@@ -25748,6 +26148,11 @@
       <c r="K423" t="n">
         <v>422</v>
       </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R423" t="inlineStr">
         <is>
           <t>PUCHNER Oliver</t>
@@ -25811,6 +26216,11 @@
       <c r="K424" t="n">
         <v>423</v>
       </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="R424" t="inlineStr">
         <is>
           <t>TRIPANO Manuel</t>
@@ -25874,6 +26284,11 @@
       <c r="K425" t="n">
         <v>424</v>
       </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R425" t="inlineStr">
         <is>
           <t>FRIEDENSON Kaelin</t>
@@ -25937,6 +26352,11 @@
       <c r="K426" t="n">
         <v>425</v>
       </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R426" t="inlineStr">
         <is>
           <t>BRZEZINSKI Jakub</t>
@@ -26000,6 +26420,11 @@
       <c r="K427" t="n">
         <v>426</v>
       </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R427" t="inlineStr">
         <is>
           <t>ECHANIZ Pau</t>
@@ -26063,6 +26488,11 @@
       <c r="K428" t="n">
         <v>427</v>
       </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="R428" t="inlineStr">
         <is>
           <t>AUBERTIN Maxime</t>
@@ -26126,6 +26556,11 @@
       <c r="K429" t="n">
         <v>428</v>
       </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R429" t="inlineStr">
         <is>
           <t>NOVAK Matyas</t>
@@ -26189,6 +26624,11 @@
       <c r="K430" t="n">
         <v>429</v>
       </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R430" t="inlineStr">
         <is>
           <t>PASIUT Michal</t>
@@ -26252,6 +26692,11 @@
       <c r="K431" t="n">
         <v>430</v>
       </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="R431" t="inlineStr">
         <is>
           <t>MARTINEZ Jesus</t>
@@ -26315,6 +26760,11 @@
       <c r="K432" t="n">
         <v>431</v>
       </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R432" t="inlineStr">
         <is>
           <t>IVCHENKO Artem</t>
@@ -26378,6 +26828,11 @@
       <c r="K433" t="n">
         <v>432</v>
       </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="R433" t="inlineStr">
         <is>
           <t>PEREZ RINCON Alexis</t>
@@ -26441,6 +26896,11 @@
       <c r="K434" t="n">
         <v>433</v>
       </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="R434" t="inlineStr">
         <is>
           <t>SAVLI Jakob</t>
@@ -26504,6 +26964,11 @@
       <c r="K435" t="n">
         <v>434</v>
       </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R435" t="inlineStr">
         <is>
           <t>ALVARENGA Frederico</t>
@@ -26567,6 +27032,11 @@
       <c r="K436" t="n">
         <v>435</v>
       </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="R436" t="inlineStr">
         <is>
           <t>MCCREERY Alistair</t>
@@ -26630,6 +27100,11 @@
       <c r="K437" t="n">
         <v>436</v>
       </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R437" t="inlineStr">
         <is>
           <t>HALCIN Martin</t>
@@ -26693,6 +27168,11 @@
       <c r="K438" t="n">
         <v>437</v>
       </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R438" t="inlineStr">
         <is>
           <t>POPE Benjamin</t>
@@ -26756,6 +27236,11 @@
       <c r="K439" t="n">
         <v>438</v>
       </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R439" t="inlineStr">
         <is>
           <t>ROELLER Tillmann</t>
@@ -26819,6 +27304,11 @@
       <c r="K440" t="n">
         <v>439</v>
       </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R440" t="inlineStr">
         <is>
           <t>OHRSTROM Isak</t>
@@ -26945,6 +27435,11 @@
       <c r="K442" t="n">
         <v>441</v>
       </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R442" t="inlineStr">
         <is>
           <t>DESNOS Mathieu</t>
@@ -27008,6 +27503,11 @@
       <c r="K443" t="n">
         <v>442</v>
       </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="R443" t="inlineStr">
         <is>
           <t>BALDONI Alex</t>
@@ -27071,6 +27571,11 @@
       <c r="K444" t="n">
         <v>443</v>
       </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R444" t="inlineStr">
         <is>
           <t>DE COSTER Gabriel</t>
@@ -27134,6 +27639,11 @@
       <c r="K445" t="n">
         <v>444</v>
       </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="R445" t="inlineStr">
         <is>
           <t>HENGST Stefan</t>
@@ -27197,6 +27707,11 @@
       <c r="K446" t="n">
         <v>445</v>
       </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R446" t="inlineStr">
         <is>
           <t>KREJCI Jakub</t>
@@ -27260,6 +27775,11 @@
       <c r="K447" t="n">
         <v>446</v>
       </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="R447" t="inlineStr">
         <is>
           <t>HOCEVAR Ziga Lin</t>
@@ -27323,6 +27843,11 @@
       <c r="K448" t="n">
         <v>447</v>
       </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R448" t="inlineStr">
         <is>
           <t>DELFOUR Lucien</t>
@@ -27386,6 +27911,11 @@
       <c r="K449" t="n">
         <v>448</v>
       </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="R449" t="inlineStr">
         <is>
           <t>OSCHMAUTZ Felix</t>
@@ -27449,6 +27979,11 @@
       <c r="K450" t="n">
         <v>449</v>
       </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="R450" t="inlineStr">
         <is>
           <t>CASTRYCK Titouan</t>
@@ -27512,6 +28047,11 @@
       <c r="K451" t="n">
         <v>450</v>
       </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R451" t="inlineStr">
         <is>
           <t>LEAVER Sam</t>
@@ -27575,6 +28115,11 @@
       <c r="K452" t="n">
         <v>451</v>
       </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R452" t="inlineStr">
         <is>
           <t>ANDERSON Timothy</t>
@@ -27638,6 +28183,11 @@
       <c r="K453" t="n">
         <v>452</v>
       </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R453" t="inlineStr">
         <is>
           <t>DICKSON Jonny</t>
@@ -27701,6 +28251,11 @@
       <c r="K454" t="n">
         <v>453</v>
       </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="R454" t="inlineStr">
         <is>
           <t>ECHEVERRIA OLGUIN Andraz</t>
@@ -27764,6 +28319,11 @@
       <c r="K455" t="n">
         <v>454</v>
       </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R455" t="inlineStr">
         <is>
           <t>ROHRER Jan</t>
@@ -27827,6 +28387,11 @@
       <c r="K456" t="n">
         <v>455</v>
       </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R456" t="inlineStr">
         <is>
           <t>MADORE Mathurin</t>
@@ -27890,6 +28455,11 @@
       <c r="K457" t="n">
         <v>456</v>
       </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R457" t="inlineStr">
         <is>
           <t>GONCALVES Pedro</t>
@@ -27953,6 +28523,11 @@
       <c r="K458" t="n">
         <v>457</v>
       </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R458" t="inlineStr">
         <is>
           <t>OCHOA Manuel</t>
@@ -28016,6 +28591,11 @@
       <c r="K459" t="n">
         <v>458</v>
       </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R459" t="inlineStr">
         <is>
           <t>HEGGE Noah</t>
@@ -28079,6 +28659,11 @@
       <c r="K460" t="n">
         <v>459</v>
       </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="R460" t="inlineStr">
         <is>
           <t>POLACZYK Mateusz</t>
@@ -28142,6 +28727,11 @@
       <c r="K461" t="n">
         <v>460</v>
       </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R461" t="inlineStr">
         <is>
           <t>LLORENTE David</t>
@@ -28205,6 +28795,11 @@
       <c r="K462" t="n">
         <v>461</v>
       </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R462" t="inlineStr">
         <is>
           <t>RENIA Benjamin</t>
@@ -28268,6 +28863,11 @@
       <c r="K463" t="n">
         <v>462</v>
       </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="R463" t="inlineStr">
         <is>
           <t>MARX Dimitri</t>
@@ -28331,6 +28931,11 @@
       <c r="K464" t="n">
         <v>463</v>
       </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="R464" t="inlineStr">
         <is>
           <t>DOUGOUD Martin</t>
@@ -28393,6 +28998,11 @@
       </c>
       <c r="K465" t="n">
         <v>464</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="R465" t="inlineStr">
         <is>
